--- a/Ошибки/Errors.xlsx
+++ b/Ошибки/Errors.xlsx
@@ -1,80 +1,147 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" r:id="Rada239d981094bf4"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="@"/>
-  </x:numFmts>
-  <x:fonts count="3">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF233C4C"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF193F50"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border/>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF233C4C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF193F50"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -269,41 +336,350 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="39" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="65" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>started_at</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>uuid</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="D1" s="6" t="str">
-        <x:v>sku (prediction)</x:v>
-      </x:c>
-      <x:c r="E1" s="6" t="str">
-        <x:v>corr sku</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="25" customHeight="1">
-      <x:c r="A2" s="3"/>
-      <x:c r="B2" s="3"/>
-      <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
-      <x:c r="E2" s="3"/>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>sku (prediction)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>corr sku</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024-07-22 12:17:49.709288</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3f0a1a41-ed61-4a39-b1c8-7fd685c0a85b</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BioTrue 120 мл</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>tovar_ne_alcon</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024-07-22 14:01:32.157711</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2796efbf-d65b-4fb6-b0d9-f6b9cd3cf29b</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Раствор ACUVUE RevitaLens 100 ml</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tovar_ne_alcon</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-07-22 14:01:32.157711</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2796efbf-d65b-4fb6-b0d9-f6b9cd3cf29b</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Раствор ACUVUE RevitaLens 100 ml</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>tovar_ne_alcon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-07-22 15:24:33.948633</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>531f0a38-960d-4653-afa7-c0f1f4ee72b9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dailies Total One Multifcal 8.5 N30 (Sph: +04.50, Add: MED, Др.: 14.1, BC: 8.5)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dailies_total1_30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>dailies_total1_multifocal_30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-07-22 19:16:11.157023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>879221a6-8e5d-438a-b948-7fc256481c0c</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PRECISION1 TORIC WHITE 8.5 -2.75 -2.25 90 30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>tovar_alcon</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>precision1_for_astigmatism_30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-07-22 19:16:11.157023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>879221a6-8e5d-438a-b948-7fc256481c0c</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PRECISION1 TORIC WHITE 8.5 -3.00 -1.75 90 30</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tovar_alcon</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>precision1_for_astigmatism_30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-07-24 08:13:14.799203</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4adae89b-4c99-46cf-929c-570b3e8f0d8c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALCON LENSES TOTAL30 8,4 SPH -2.75        </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>total30_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-07-24 08:13:14.799203</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4adae89b-4c99-46cf-929c-570b3e8f0d8c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALCON LENSES TOTAL30 8,4 SPH -2.75        </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>total30_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-07-25 18:05:29.893954</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>feccc66f-69a1-4bb5-a74d-59b2a6b5d7a5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dailes Total1 (-6 / 8,5)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dailies_total1_30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-07-26 21:43:18.004217</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>e6bf6209-38e3-4ecc-8fe3-549c5a888848</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TOTAL30 (1шт.)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>total30_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-07-27 09:11:40.443845</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8f534e69-8964-4a00-93be-987fb8092f04</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TOTAL30 (3шт.)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>total30_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-07-28 18:56:21.316999</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>9ed846d6-119b-4d94-8014-b6c51242fd72</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TOTAL30 (3 pk)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>total30_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024-07-28 18:56:21.316999</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9ed846d6-119b-4d94-8014-b6c51242fd72</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TOTAL30 (3 pk)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>total30_3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>